--- a/suggestions/WG7TF2-suggestions-sheet.xlsx
+++ b/suggestions/WG7TF2-suggestions-sheet.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Lists (generated)" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Suggestions (brief)" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Lists (generated)" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Suggestions (brief)" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -18,7 +18,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="5">
+  <fonts count="6">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -34,6 +34,10 @@
       <b val="1"/>
     </font>
     <font>
+      <sz val="10"/>
+    </font>
+    <font>
+      <i val="1"/>
       <sz val="10"/>
     </font>
     <font>
@@ -66,14 +70,17 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -441,7 +448,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E17"/>
+  <dimension ref="A1:E18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="46" customWidth="1" min="1" max="1"/>
@@ -488,7 +495,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>V1 · Research that is visible, valued, impactful (brief v0.1)</t>
+          <t>V1 · Research that is visible, valued, impactful (brief v0.2)</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -515,7 +522,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>A1 · Quality &amp; Trust (brief v0.1)</t>
+          <t>A1 · Quality &amp; Trust (brief v0.2)</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -537,7 +544,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>A2 · Collaboration &amp; Innovation (brief v0.1)</t>
+          <t>A2 · Collaboration &amp; Innovation (brief v0.2)</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -559,7 +566,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>A3 · Impact &amp; Relevance (brief v0.1)</t>
+          <t>A3 · Impact &amp; Relevance (brief v0.2)</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -576,7 +583,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>B1 · Research Output Quality &amp; Traceability (brief v0.1)</t>
+          <t>B1 · Research Output Quality &amp; Traceability (brief v0.2)</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -593,7 +600,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>B2 · Governance, Ethics &amp; Compliance (brief v0.1)</t>
+          <t>B2 · Governance, Ethics &amp; Compliance (brief v0.2)</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -610,7 +617,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>B8 · Integrity &amp; Accountability (brief v0.1)</t>
+          <t>B8 · Integrity &amp; Accountability (brief v0.2)</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -622,7 +629,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>B3 · Capacity Building &amp; Inclusive Training (brief v0.1)</t>
+          <t>B3 · Capacity Building &amp; Inclusive Training (brief v0.2)</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -634,7 +641,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>B4 · Interoperability &amp; Metadata Quality (brief v0.1)</t>
+          <t>B4 · Interoperability &amp; Metadata Quality (brief v0.2)</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -646,7 +653,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>B7 · Infrastructure &amp; Technical Enablement (brief v0.1)</t>
+          <t>B7 · Infrastructure &amp; Technical Enablement (brief v0.2)</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -658,7 +665,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>B5 · Evaluation for Learning &amp; Responsibility (brief v0.1)</t>
+          <t>B9 · Strategic Steering &amp; Institutional Autonomy (brief v0.2)</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -670,7 +677,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>B6 · Visibility, Equity &amp; Societal Relevance (brief v0.1)</t>
+          <t>B5 · Evaluation for Learning &amp; Responsibility (brief v0.2)</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -682,21 +689,28 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>O1 · Trustworthy Research (brief v0.1)</t>
+          <t>B6 · Visibility, Equity &amp; Societal Relevance (brief v0.2)</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>O2 · Sustainable Innovation (brief v0.1)</t>
+          <t>O1 · Trustworthy Research (brief v0.2)</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>O3 · Societal Impact (brief v0.1)</t>
+          <t>O2 · Sustainable Innovation (brief v0.2)</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>O3 · Societal Impact (brief v0.2)</t>
         </is>
       </c>
     </row>
@@ -711,7 +725,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K2"/>
+  <dimension ref="A1:K3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -734,81 +748,89 @@
         </is>
       </c>
     </row>
-    <row r="2" ht="30" customHeight="1">
+    <row r="2" ht="32" customHeight="1">
       <c r="A2" s="4" t="inlineStr">
         <is>
+          <t>You do not have to fill in a row to say something. You can also leave a comment on any cell (Insert &gt; Comment), or reply to someone else's, and the coordinators read those alongside the rows. The same contribution terms apply to anything you leave in a comment.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="30" customHeight="1">
+      <c r="A3" s="5" t="inlineStr">
+        <is>
           <t>Date</t>
         </is>
       </c>
-      <c r="B2" s="4" t="inlineStr">
+      <c r="B3" s="5" t="inlineStr">
         <is>
           <t>Name / affiliation</t>
         </is>
       </c>
-      <c r="C2" s="4" t="inlineStr">
+      <c r="C3" s="5" t="inlineStr">
         <is>
           <t>Node</t>
         </is>
       </c>
-      <c r="D2" s="4" t="inlineStr">
+      <c r="D3" s="5" t="inlineStr">
         <is>
           <t>What are you contributing?</t>
         </is>
       </c>
-      <c r="E2" s="4" t="inlineStr">
+      <c r="E3" s="5" t="inlineStr">
         <is>
           <t>Type of change</t>
         </is>
       </c>
-      <c r="F2" s="4" t="inlineStr">
+      <c r="F3" s="5" t="inlineStr">
         <is>
           <t>Suggestion</t>
         </is>
       </c>
-      <c r="G2" s="4" t="inlineStr">
+      <c r="G3" s="5" t="inlineStr">
         <is>
           <t>Why</t>
         </is>
       </c>
-      <c r="H2" s="4" t="inlineStr">
+      <c r="H3" s="5" t="inlineStr">
         <is>
           <t>Perspective</t>
         </is>
       </c>
-      <c r="I2" s="4" t="inlineStr">
+      <c r="I3" s="5" t="inlineStr">
         <is>
           <t>Example</t>
         </is>
       </c>
-      <c r="J2" s="4" t="inlineStr">
+      <c r="J3" s="5" t="inlineStr">
         <is>
           <t>I agree to the terms</t>
         </is>
       </c>
-      <c r="K2" s="4" t="inlineStr">
+      <c r="K3" s="5" t="inlineStr">
         <is>
           <t>Status (coordinators)</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="1">
+  <mergeCells count="2">
+    <mergeCell ref="A2:K2"/>
     <mergeCell ref="A1:K1"/>
   </mergeCells>
   <dataValidations count="5">
-    <dataValidation sqref="C3:C300" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Not on the list" error="Pick one of the offered values. They come from the WG7-TF2 taxonomy, so answers can be matched with the ones filed through GitHub." type="list">
-      <formula1>'Lists (generated)'!$A$3:$A$17</formula1>
+    <dataValidation sqref="C4:C300" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Not on the list" error="Pick one of the offered values. They come from the WG7-TF2 taxonomy, so answers can be matched with the ones filed through GitHub." type="list">
+      <formula1>'Lists (generated)'!$A$3:$A$18</formula1>
     </dataValidation>
-    <dataValidation sqref="D3:D300" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Not on the list" error="Pick one of the offered values. They come from the WG7-TF2 taxonomy, so answers can be matched with the ones filed through GitHub." type="list">
+    <dataValidation sqref="D4:D300" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Not on the list" error="Pick one of the offered values. They come from the WG7-TF2 taxonomy, so answers can be matched with the ones filed through GitHub." type="list">
       <formula1>'Lists (generated)'!$B$3:$B$5</formula1>
     </dataValidation>
-    <dataValidation sqref="E3:E300" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Not on the list" error="Pick one of the offered values. They come from the WG7-TF2 taxonomy, so answers can be matched with the ones filed through GitHub." type="list">
+    <dataValidation sqref="E4:E300" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Not on the list" error="Pick one of the offered values. They come from the WG7-TF2 taxonomy, so answers can be matched with the ones filed through GitHub." type="list">
       <formula1>'Lists (generated)'!$C$3:$C$8</formula1>
     </dataValidation>
-    <dataValidation sqref="H3:H300" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Not on the list" error="Pick one of the offered values. They come from the WG7-TF2 taxonomy, so answers can be matched with the ones filed through GitHub." type="list">
+    <dataValidation sqref="H4:H300" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Not on the list" error="Pick one of the offered values. They come from the WG7-TF2 taxonomy, so answers can be matched with the ones filed through GitHub." type="list">
       <formula1>'Lists (generated)'!$D$3:$D$14</formula1>
     </dataValidation>
-    <dataValidation sqref="J3:J300" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Not on the list" error="Pick one of the offered values. They come from the WG7-TF2 taxonomy, so answers can be matched with the ones filed through GitHub." type="list">
+    <dataValidation sqref="J4:J300" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Not on the list" error="Pick one of the offered values. They come from the WG7-TF2 taxonomy, so answers can be matched with the ones filed through GitHub." type="list">
       <formula1>'Lists (generated)'!$E$3:$E$3</formula1>
     </dataValidation>
   </dataValidations>
